--- a/DataTables/DetailText/剧情/025_03治疗失败.xlsx
+++ b/DataTables/DetailText/剧情/025_03治疗失败.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C1FD791-1E60-4A59-99E8-0ECD0C22E0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2075D2-D199-4436-A4F3-129150CBCD8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19740" yWindow="5400" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -333,7 +333,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -347,7 +347,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -368,7 +368,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -549,7 +549,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -828,28 +828,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="29.5" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="11.625" customWidth="1"/>
+    <col min="1" max="1" width="7.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.265625" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="20" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="20" customFormat="1">
       <c r="A1" s="13" t="s">
         <v>19</v>
       </c>
@@ -1040,14 +1037,14 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="56.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.73046875" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
